--- a/astro-site/public/dl/catering-checklist-templates/09-catering-deposits-invoicing-payments.xlsx
+++ b/astro-site/public/dl/catering-checklist-templates/09-catering-deposits-invoicing-payments.xlsx
@@ -855,7 +855,7 @@
     <row r="11" ht="48" customHeight="1">
       <c r="B11" s="47" t="inlineStr">
         <is>
-          <t>▸ Go through it with the calendar in hand: the "When" column counts DAYS before the event (15 days out, 7 days out, 3 days out, day before), not hours. Nothing leaves here without a quote accepted in writing and the deposit collected and logged.</t>
+          <t>▸ Go through it with the calendar in hand: the "When" column counts DAYS before the event (By 15 days out, By 7 days out, By 3 days out, Day before: deadlines), not hours. Nothing leaves here without a quote accepted in writing and the deposit collected and logged.</t>
         </is>
       </c>
     </row>
@@ -887,10 +887,10 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="78" customHeight="1">
+    <row r="20" ht="108" customHeight="1">
       <c r="B20" s="47" t="inlineStr">
         <is>
-          <t>▸ What carries sales tax is decided by your state (check with your CPA or the department of revenue): in many states food, drinks, rentals and the mandatory service charge. A mandatory service charge is NOT a gratuity: for the IRS it is wages (Rev. Rul. 2012-18); the gratuity is the client's choice, goes on a separate line and belongs to the team. A tax-exempt client needs their exemption certificate on file. If the two subtotals don't add up to quote + extras, the sheet warns you.</t>
+          <t>▸ What carries sales tax is decided by your state (check with your CPA or the department of revenue): in many states food, drinks, rentals and the mandatory service charge. A mandatory service charge is NOT a tip: it is your revenue, and whatever part of it you pay to staff is wages on payroll for the IRS, not tips (Rev. Rul. 2012-18). Some states (e.g., NY, MA) presume an undisclosed service charge belongs to staff: state your policy in the contract. The gratuity is the client's choice, goes on a separate line and belongs to the team. A tax-exempt client needs their exemption certificate on file. If the two subtotals don't add up to quote + extras, the sheet warns you.</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
     <row r="22" ht="93" customHeight="1">
       <c r="B22" s="47" t="inlineStr">
         <is>
-          <t>▸ If the event had a bar with CASH payment, count the money in the optional table at the bottom (denominations, minus the starting bank) and, if you like, add that net cash to "Paid after the event" yourself. It is not linked on purpose: most events have no cash, and a fixed formula would leave a 0 subtracting where it shouldn't. The cash table has US bills and coins ($100 … 1¢; a "25¢ roll" counts $10 and a "10¢ roll" $5); in the UK, Canada or Australia, unprotect the sheet (no password) and change each row's label and value.</t>
+          <t>▸ If the event had a bar with CASH payment, count the money in the optional table at the bottom (denominations, minus the starting bank) and, if you like, add that net cash to "Paid after the event" yourself. It is not linked on purpose: most events have no cash, and a fixed formula would leave a 0 subtracting where it shouldn't. The cash table has US bills and coins ($100 … 1¢; a "25¢ roll" counts $10 and a "10¢ roll" $5); in the UK, Canada or Australia, unprotect the sheet (no password) and change each row's label and the multiplier in its Subtotal formula.</t>
         </is>
       </c>
     </row>
@@ -950,10 +950,10 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="32" customHeight="1">
+    <row r="35" ht="47" customHeight="1">
       <c r="B35" s="47" t="inlineStr">
         <is>
-          <t>▸ "N/A" = not applicable at your commissary: that task comes OUT of the total (don't delete it, mark it N/A). "—" = not done: it still counts as pending and lowers the percentage, which is the point.</t>
+          <t>▸ "N/A" = doesn't apply (to this event, or to your commissary): that task comes OUT of the total (don't delete it, mark it N/A). "—" = not done: it still counts as pending and lowers the percentage, which is the point.</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D5" s="50" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>By 15 days out</t>
         </is>
       </c>
       <c r="E5" s="50" t="n"/>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="B6" s="52" t="inlineStr">
         <is>
-          <t>Guaranteed count (final headcount) confirmed and the deadline for changes sent to the client in writing</t>
+          <t>Deadline for the guaranteed count (final headcount) sent to the client in writing; the count locks on that date, per your contract</t>
         </is>
       </c>
       <c r="C6" s="50" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D6" s="50" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>By 15 days out</t>
         </is>
       </c>
       <c r="E6" s="50" t="n"/>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="D7" s="50" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>By 15 days out</t>
         </is>
       </c>
       <c r="E7" s="50" t="n"/>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="D8" s="50" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>By 15 days out</t>
         </is>
       </c>
       <c r="E8" s="50" t="n"/>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="D9" s="50" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>By 15 days out</t>
         </is>
       </c>
       <c r="E9" s="50" t="n"/>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D10" s="50" t="inlineStr">
         <is>
-          <t>15 days out</t>
+          <t>By 15 days out</t>
         </is>
       </c>
       <c r="E10" s="50" t="n"/>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="50" t="inlineStr">
         <is>
-          <t>7 days out</t>
+          <t>By 7 days out</t>
         </is>
       </c>
       <c r="E11" s="50" t="n"/>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="D12" s="50" t="inlineStr">
         <is>
-          <t>7 days out</t>
+          <t>By 7 days out</t>
         </is>
       </c>
       <c r="E12" s="50" t="n"/>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="D13" s="50" t="inlineStr">
         <is>
-          <t>7 days out</t>
+          <t>By 7 days out</t>
         </is>
       </c>
       <c r="E13" s="50" t="n"/>
@@ -1373,7 +1373,7 @@
       </c>
       <c r="D14" s="50" t="inlineStr">
         <is>
-          <t>7 days out</t>
+          <t>By 7 days out</t>
         </is>
       </c>
       <c r="E14" s="50" t="n"/>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="D15" s="50" t="inlineStr">
         <is>
-          <t>3 days out</t>
+          <t>By 3 days out</t>
         </is>
       </c>
       <c r="E15" s="50" t="n"/>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="B8" s="52" t="inlineStr">
         <is>
-          <t>Breakage or incident charges communicated to the client before invoicing, not inside the invoice</t>
+          <t>Breakage or incident charges communicated to the client before the invoice goes out, so they never show up on it as a surprise</t>
         </is>
       </c>
       <c r="C8" s="50" t="inlineStr">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="22" customHeight="1">
+    <row r="10" ht="30.5" customHeight="1">
       <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Accepted quote (before tax)</t>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="D10" s="20" t="inlineStr">
         <is>
-          <t>The accepted amount BEFORE sales tax.</t>
+          <t>The accepted amount BEFORE sales tax, mandatory service charge included if your quote has one.</t>
         </is>
       </c>
     </row>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="30.5" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Sales tax (rate in Event Billing Log C3)</t>
+          <t>Sales tax (rate set in Event Billing Log C3)</t>
         </is>
       </c>
       <c r="B15" s="15" t="n"/>
@@ -2211,14 +2211,14 @@
       </c>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>Formula.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
+          <t>Formula: taxable subtotal × the rate in Event Billing Log C3. It stays at $0 until you enter your rate there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30.5" customHeight="1">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Tax on the non-taxable subtotal (0)</t>
+          <t>Non-taxable subtotal: no sales tax</t>
         </is>
       </c>
       <c r="B16" s="15" t="n"/>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>Formula.</t>
+          <t>Always $0: exempt items and tax-exempt clients carry no sales tax. Nothing to enter.</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
     <row r="3" ht="30.5" customHeight="1">
       <c r="A3" s="37" t="inlineStr">
         <is>
-          <t>Sales tax rate (state + local)</t>
+          <t>Sales tax rate (state + local) — set it first</t>
         </is>
       </c>
       <c r="C3" s="66" t="n">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="D3" s="30" t="inlineStr">
         <is>
-          <t>Your combined rate (state + local), e.g. 0.0825 for 8.25%. "Event Settlement" applies it to the taxable subtotal; here it is applied to the whole base, so "Invoice total" is an estimate if part of the event is exempt: the exact figure is in "Event Settlement".</t>
+          <t>0 = no sales tax until you enter your combined rate (state + local), e.g. 0.0825 for 8.25%. "Event Settlement" applies it to the taxable subtotal; here it is applied to the whole base, so "Invoice total" is an estimate if part of the event is exempt: the exact figure is in "Event Settlement".</t>
         </is>
       </c>
     </row>
